--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="45" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" state="visible" r:id="rId1"/>
@@ -65,7 +64,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,16 +73,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="13"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -95,16 +106,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFd9e1f2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFfff2cc"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -112,27 +123,76 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFc6c6c6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFc6c6c6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFc6c6c6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -211,10 +271,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -252,69 +312,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -338,54 +400,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -395,7 +456,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -404,7 +465,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -413,7 +474,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -421,10 +482,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -453,7 +514,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -466,13 +527,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -492,867 +552,1138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="80.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PS Tool Workbook -- iba/app/ps scripts</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="60" customFormat="1" customHeight="1" s="3">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Escalation #1004. One tab per script, modeled on the researcher's own 'escalation actions worksheet.xlsx' -- row 4 = flag headers, row 6 = fill in the cells your call needs (leave the rest blank), column B compiles the full command for copy/paste into the terminal. Escalation.ps1 itself is not duplicated here -- use the existing model sheet for that one.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Script</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Behaviour.ps1</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>List behaviour rules (cfg_behaviour_class/cfg_behaviour_rule).</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Book-Narrative.ps1</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Run the book-narrative step for a book.</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+    </row>
+    <row r="7" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>BookNarrative-Generate.ps1</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Generate the book-narrative draft.</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+    </row>
+    <row r="8" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>BookNarrative-Validate.ps1</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Validate a book-narrative file.</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+    </row>
+    <row r="9" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Build-Passages.ps1</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Build passage rows from a payload.</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+    </row>
+    <row r="10" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Candidate-Curate.ps1</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Curate candidate_seed rows (tag/decide/split/delete).</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+    </row>
+    <row r="11" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Candidate-Quality.ps1</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>candidate_seed quality-check report.</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Chapter-Generate.ps1</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Generate a chapter-level output.</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Cluster-Assign.ps1</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Assign strongs to M-code clusters / validate assignment.</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Cluster-Report.ps1</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Cluster overview report.</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+    </row>
+    <row r="15" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Config-Maintenance.ps1</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>THE sanctioned path for changing a cfg_* row.</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>ContentIndex-Rebuild.ps1</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Rebuild the content search index.</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>ContentIndex-Search.ps1</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Query the content search index.</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>ContentIndex-SizeProfile.ps1</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Size-profile the content index.</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>create-iba-view-template.ps1</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Create/replace a named SQLite view in iba.db.</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>create-passage-view-and-export.ps1</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Create vw_passage_verse_top10 and export it to CSV.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+    </row>
+    <row r="21" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>create-passages-by-book-view-and-export.ps1</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Create vw_passages_by_book (scoped to one book) and export it.</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+    </row>
+    <row r="22" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Debate-Run.ps1</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>The debate pipeline (HIB/phenomenon/operation/closing) for a book.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+    </row>
+    <row r="23" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Escalation.ps1</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>See the researcher's own model sheet, 'escalation actions worksheet.xlsx' -- not rebuilt here, this tab is a pointer only.</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+    </row>
+    <row r="24" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>export-iba-config-tables.ps1</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Export all cfg_* tables to CSV + an index report.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+    </row>
+    <row r="25" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Export-Tables.ps1</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Export one or more cfg_*/data tables to CSV.</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+    </row>
+    <row r="26" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>FolderPurpose.ps1</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>The folder_purpose governance mechanism (Methods A-D).</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+    </row>
+    <row r="27" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>generate-iba-db-schema-report.ps1</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Generate the full iba.db schema overview doc.</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+    </row>
+    <row r="28" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Lexicon-Parse.ps1</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Parse strong_lexicon / related-word data.</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="12" t="n"/>
+    </row>
+    <row r="29" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Log-Retention.ps1</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Apply log-retention rules (prune old logs).</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+    </row>
+    <row r="30" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Manifest-Rebuild.ps1</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Rebuild the file_manifest table.</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+    </row>
+    <row r="31" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Manifest-Search.ps1</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Search the file_manifest table.</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+    </row>
+    <row r="32" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>New-Word.ps1</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Register a new word_registry entry and run its first-pass pipeline.</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+    </row>
+    <row r="33" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Operations-Ingest.ps1</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Ingest a debate-step payload (hib/phenomenon/operation/closing).</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Passage-Quality.ps1</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Quality-check passages, optionally scoped to a book.</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+    </row>
+    <row r="35" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>PassageDebate-Report.ps1</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Report on passage/debate state for a book.</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+    </row>
+    <row r="36" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>PassageDebate-Sync.ps1</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Sync file-based debate output back into passage/phenomenon.</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+    </row>
+    <row r="37" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>PathAudit.ps1</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Scan for hardcoded paths that should be config-driven.</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+    </row>
+    <row r="38" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Prose.ps1</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Prose store: extract/search/export/import/flag/status the programme prose.</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="12" t="n"/>
+    </row>
+    <row r="39" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Raw-Backfill.ps1</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Backfill span/strong_verse from raw span data for a book.</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="12" t="n"/>
+    </row>
+    <row r="40" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Registry-Report.ps1</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>word_registry overview report.</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="12" t="n"/>
+    </row>
+    <row r="41" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Reports.ps1</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Word/book validation and report bundle.</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="C41" s="12" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="12" t="n"/>
+    </row>
+    <row r="42" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>SchemaOverview-Report.ps1</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Live iba.db schema overview report.</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>SeedCandidate-Report.ps1</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>candidate_seed coverage report.</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="C43" s="12" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="12" t="n"/>
+    </row>
+    <row r="44" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Set-Candidates.ps1</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>Seed candidate_seed rows for a book.</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="12" t="n"/>
+    </row>
+    <row r="45" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>SpanAnalysis-Report.ps1</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>span table analysis report.</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="C45" s="12" t="n"/>
+      <c r="D45" s="12" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="12" t="n"/>
+    </row>
+    <row r="46" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Start-Iba.ps1</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>Session bootstrap -- run once per session before any IBA work.</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="C46" s="12" t="n"/>
+      <c r="D46" s="12" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="12" t="n"/>
+    </row>
+    <row r="47" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>StrongMeaning-Report.ps1</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="C47" s="12" t="n"/>
+      <c r="D47" s="12" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="12" t="n"/>
+    </row>
+    <row r="48" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>StrongVerse-Report.ps1</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>Report a word's strong&lt;-&gt;verse coverage.</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="12" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="12" t="n"/>
+    </row>
+    <row r="49" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>VerseLexical.ps1</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>Run verse_lexical (L4b) derivation for a book/chapter range.</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="12" t="n"/>
+    </row>
+    <row r="50" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>VerseSpanMeaning-Report.ps1</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>Report verse-span-meaning coverage for a book.</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="12" t="n"/>
+    </row>
+    <row r="51" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>WholeBookRead-Report.ps1</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>Whole-book-read report for a book.</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="12" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="12" t="n"/>
+    </row>
+    <row r="52" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>WordRegistrySpan-Report.ps1</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>Report a word's span coverage against its registry entry.</t>
         </is>
       </c>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cluster-Assign.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Assign strongs to M-code clusters / validate assignment.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Step</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Assign|Validate</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Cluster-Assign.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cluster-Report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Cluster overview report.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Cluster-Report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="9" max="9"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Config-Maintenance.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>THE sanctioned path for changing a cfg_* row.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Step</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Table</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Op</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Where</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-Set</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-Question</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Validate|Propose|Report</t>
@@ -1388,319 +1719,399 @@
           <t>resume a specific paused proposal</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="J5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Config-Maintenance.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6&lt;&gt;"",$J$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ContentIndex-Rebuild.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Rebuild the content search index.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\ContentIndex-Rebuild.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ContentIndex-Search.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Query the content search index.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Query</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Csv</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>output as CSV</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\ContentIndex-Search.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ContentIndex-SizeProfile.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Size-profile the content index.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\ContentIndex-SizeProfile.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>create-iba-view-template.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Create/replace a named SQLite view in iba.db.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-DbPath</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-ViewName</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Apply</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-ReplaceExisting</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>default: iba/app/db/iba.db</t>
@@ -1716,96 +2127,118 @@
           <t>actually create/replace the view</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="F5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\create-iba-view-template.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>create-passage-view-and-export.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Create vw_passage_verse_top10 and export it to CSV.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-DbPath</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-ViewName</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-OutDir</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-CsvFileName</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-DryRun</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>default: iba/app/db/iba.db</t>
@@ -1826,102 +2259,127 @@
           <t>default: vw_passage_verse_top10.csv</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="G5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\create-passage-view-and-export.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>create-passages-by-book-view-and-export.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Create vw_passages_by_book (scoped to one book) and export it.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-DbPath</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-ViewName</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-OutDir</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-CsvFileName</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-DryRun</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>default: iba/app/db/iba.db</t>
@@ -1942,108 +2400,141 @@
           <t>default: iba/app/config/views</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\create-passages-by-book-view-and-export.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Debate-Run.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>The debate pipeline (HIB/phenomenon/operation/closing) for a book.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Chapters</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Range</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-BookLabel</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-Step</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>hib.set|passage.build|phenomenon.set|operation.set|closing.set</t>
@@ -2054,78 +2545,97 @@
           <t>resume a specific run</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="I5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Debate-Run.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" "&amp;G6&amp;" ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Behaviour.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>List behaviour rules (cfg_behaviour_class/cfg_behaviour_rule).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Action</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Class</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>List</t>
@@ -2137,46 +2647,58 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Behaviour.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" "&amp;D6&amp;" ")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="12" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Escalation.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>See the researcher's own 'escalation actions worksheet.xlsx' -- that sheet already covers this script in full (Raise/Update/AnswerRun/etc) and is the model this whole workbook is based on. Not duplicated here.</t>
         </is>
@@ -2186,74 +2708,89 @@
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>export-iba-config-tables.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Export all cfg_* tables to CSV + an index report.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-DbPath</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-OutDir</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-ReportFileName</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-TableLike</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>default: iba/app/db/iba.db</t>
@@ -2275,89 +2812,117 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\export-iba-config-tables.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Export-Tables.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Export one or more cfg_*/data tables to CSV.</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="G2" s="12" t="n"/>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Out</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Table</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
-    </row>
-    <row r="5">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>-Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>output directory override</t>
@@ -2368,114 +2933,149 @@
           <t>one or more table names, comma-separated -- repeat flag manually if needed</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>registered project database (default: iba) -- e.g. bible_research</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Export-Tables.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+      <c r="B6" s="7">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" "&amp;G6&amp;" ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="9" max="9"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>FolderPurpose.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>The folder_purpose governance mechanism (Methods A-D).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Action</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-FolderPath</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Type</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Status</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-UsageDescription</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-TopLevelRoot</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Seed|CrossCheck|AutoAssess|Set|List|Show</t>
@@ -2496,84 +3096,109 @@
           <t>authoritative|mixed|reallocate|stale|deleted</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\FolderPurpose.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" "&amp;F6&amp;" ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6&lt;&gt;"",$J$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>generate-iba-db-schema-report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Generate the full iba.db schema overview doc.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-DbPath</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-OutDir</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-BaseName</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>default: iba/app/db/iba.db</t>
@@ -2590,395 +3215,483 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\generate-iba-db-schema-report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Lexicon-Parse.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Parse strong_lexicon / related-word data.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Step</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Parse|Related|Validate</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Lexicon-Parse.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Log-Retention.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Apply log-retention rules (prune old logs).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Log-Retention.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Manifest-Rebuild.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Rebuild the file_manifest table.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Manifest-Rebuild.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Manifest-Search.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Search the file_manifest table.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Query</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>e.g. grace, or registry:68, or type:observations</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Manifest-Search.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>New-Word.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Register a new word_registry entry and run its first-pass pipeline.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Word</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Source</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Fresh</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>the English word, e.g. compassion</t>
@@ -3000,739 +3713,952 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\New-Word.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Book-Narrative.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Run the book-narrative step for a book.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-BookLabel</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Book-Narrative.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Operations-Ingest.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Ingest a debate-step payload (hib/phenomenon/operation/closing).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Step</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Chapters</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Range</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-PayloadPath</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>hib.set|phenomenon.set|operation.set|closing.set</t>
         </is>
       </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>path to the payload JSON</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Operations-Ingest.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Passage-Quality.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Quality-check passages, optionally scoped to a book.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>omit for all books</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Passage-Quality.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PassageDebate-Report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Report on passage/debate state for a book.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Chapters</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Range</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-BookLabel</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\PassageDebate-Report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PassageDebate-Sync.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Sync file-based debate output back into passage/phenomenon.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Chapters</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Range</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-BookLabel</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\PassageDebate-Sync.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PathAudit.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Scan for hardcoded paths that should be config-driven.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Action</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Scan</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\PathAudit.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="9" max="9"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="10" max="10"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="11" max="11"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="12" max="12"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="13" max="13"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="14" max="14"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="15" max="15"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="16" max="16"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="17" max="17"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="18" max="18"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="19" max="19"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="20" max="20"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="21" max="21"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="22" max="22"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Prose.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="8" t="n"/>
+      <c r="M1" s="8" t="n"/>
+      <c r="N1" s="8" t="n"/>
+      <c r="O1" s="8" t="n"/>
+      <c r="P1" s="8" t="n"/>
+      <c r="Q1" s="8" t="n"/>
+      <c r="R1" s="8" t="n"/>
+      <c r="S1" s="8" t="n"/>
+      <c r="T1" s="8" t="n"/>
+      <c r="U1" s="8" t="n"/>
+      <c r="V1" s="8" t="n"/>
+      <c r="W1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Prose store: extract/search/export/import/flag/status the programme prose.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="8" t="n"/>
+      <c r="Q3" s="8" t="n"/>
+      <c r="R3" s="8" t="n"/>
+      <c r="S3" s="8" t="n"/>
+      <c r="T3" s="8" t="n"/>
+      <c r="U3" s="8" t="n"/>
+      <c r="V3" s="8" t="n"/>
+      <c r="W3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Step</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Chapter</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-TypeId</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-IncludeBody</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-AlsoMarkdown</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>-AlsoDocx</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>-Query</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>-Limit</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>-Fts</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>-InputFile</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>-Author</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>-FlagCode</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>-Description</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>-Find</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>-Replace</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
+      <c r="S4" s="6" t="inlineStr">
         <is>
           <t>-ProposalFile</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="T4" s="6" t="inlineStr">
         <is>
           <t>-SectionIds</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="U4" s="6" t="inlineStr">
         <is>
           <t>-Status</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>-Out</t>
         </is>
       </c>
-      <c r="W4" s="5" t="inlineStr">
+      <c r="W4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Extract|Search|ExportChapter|ImportChapter|Flag|FlagFixPropose|FlagFixApply|SetStatus</t>
@@ -3743,11 +4669,15 @@
           <t>Programme|Detail design|Findings|Essays</t>
         </is>
       </c>
+      <c r="E5" s="12" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>prose_section_type.id</t>
         </is>
       </c>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Search</t>
@@ -3768,6 +4698,9 @@
           <t>ImportChapter</t>
         </is>
       </c>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="12" t="n"/>
+      <c r="P5" s="12" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>FlagFixPropose</t>
@@ -3798,688 +4731,875 @@
           <t>override output path</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="W5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Prose.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" "&amp;F6&amp;" ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" "&amp;K6&amp;" ")&amp;IF(L6&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" "&amp;U6&amp;" ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6&lt;&gt;"",$W$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="n"/>
+      <c r="O6" s="12" t="n"/>
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="12" t="n"/>
+      <c r="T6" s="12" t="n"/>
+      <c r="U6" s="12" t="n"/>
+      <c r="V6" s="12" t="n"/>
+      <c r="W6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:W2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Raw-Backfill.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Backfill span/strong_verse from raw span data for a book.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Range</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>e.g. 1-9 (chapters)</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Raw-Backfill.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Registry-Report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>word_registry overview report.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Registry-Report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Reports.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Word/book validation and report bundle.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Step</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Word</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>ReportWord|ValidationWord|ValidationBook</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Reports.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SchemaOverview-Report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Live iba.db schema overview report.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\SchemaOverview-Report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BookNarrative-Generate.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Generate the book-narrative draft.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-BookLabel</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\BookNarrative-Generate.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SeedCandidate-Report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>candidate_seed coverage report.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\SeedCandidate-Report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Set-Candidates.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Seed candidate_seed rows for a book.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Set-Candidates.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SpanAnalysis-Report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>span table analysis report.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\SpanAnalysis-Report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Start-Iba.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Session bootstrap -- run once per session before any IBA work.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Reload</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Reset</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>reseed config from source</t>
@@ -4491,1003 +5611,1305 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Start-Iba.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>StrongMeaning-Report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\StrongMeaning-Report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>StrongVerse-Report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Report a word's strong&lt;-&gt;verse coverage.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Word</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Strong</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>e.g. H2734</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\StrongVerse-Report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="11.43357142857143" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>VerseLexical.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Run verse_lexical (L4b) derivation for a book/chapter range.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+          <t>Run verse_lexical (L4b) derivation for a book/chapter range -- covers both lexical.build and report.verse_lexical.</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="n"/>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Chapters</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Range</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-BookLabel</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
-    </row>
-    <row r="5">
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>e.g. 1,3,5 or 1-9</t>
+          <t>whole chapter(s): a single chapter e.g. 1, or a contiguous range e.g. 1-9 -- NOT a comma-list</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>e.g. 1-9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+          <t>chapter:verse[-verse] -- MUST include the colon, e.g. 8:2 (single verse) or 8:1-27 (span)</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>lexical.build|report.verse_lexical -- omit to run both chained; report.verse_lexical alone VIEWS already-built results with no re-build</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32.25" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\VerseLexical.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
+      <c r="B6" s="7">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Rom</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>8:2</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>VerseSpanMeaning-Report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Report verse-span-meaning coverage for a book.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Chapters</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Range</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-BookLabel</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\VerseSpanMeaning-Report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>WholeBookRead-Report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Whole-book-read report for a book.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-BookLabel</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\WholeBookRead-Report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>WordRegistrySpan-Report.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Report a word's span coverage against its registry entry.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Word</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\WordRegistrySpan-Report.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BookNarrative-Validate.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Validate a book-narrative file.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Path</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>path to the narrative file</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="D5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\BookNarrative-Validate.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Build-Passages.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Build passage rows from a payload.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Chapters</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Range</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-PayloadPath</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>path to the payload JSON</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="G5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Build-Passages.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="9" max="9"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="10" max="10"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Candidate-Curate.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Curate candidate_seed rows (tag/decide/split/delete).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Mode</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-LemmaKey</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Field</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-StrongVariant</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-Value</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-InputFile</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>-Question</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Curate|Load</t>
         </is>
       </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>tag|decision|split|delete</t>
         </is>
       </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Load</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Candidate-Curate.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6&lt;&gt;"",$K$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Candidate-Quality.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>candidate_seed quality-check report.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Candidate-Quality.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
+    <col width="60.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="22.005" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Chapter-Generate.ps1</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="3">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Generate a chapter-level output.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>-Book</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>-Chapters</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>-Range</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>-BookLabel</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>iba\app\ps\Chapter-Generate.ps1</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
         <v/>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -55,6 +55,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseSpanMeaning-Report" sheetId="47" state="visible" r:id="rId47"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WholeBookRead-Report" sheetId="48" state="visible" r:id="rId48"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WordRegistrySpan-Report" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Report" sheetId="50" state="visible" r:id="rId50"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64,7 +65,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,6 +95,23 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00006100"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -149,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -189,6 +207,27 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -560,7 +599,7 @@
   <cols>
     <col width="34.005" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
     <col width="80.005" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="24" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
@@ -604,7 +643,11 @@
           <t>Purpose</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
@@ -620,7 +663,11 @@
           <t>List behaviour rules (cfg_behaviour_class/cfg_behaviour_rule).</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="12" t="n"/>
       <c r="F5" s="12" t="n"/>
@@ -636,7 +683,11 @@
           <t>Run the book-narrative step for a book.</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="12" t="n"/>
       <c r="F6" s="12" t="n"/>
@@ -652,7 +703,11 @@
           <t>Generate the book-narrative draft.</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="12" t="n"/>
       <c r="F7" s="12" t="n"/>
@@ -668,7 +723,11 @@
           <t>Validate a book-narrative file.</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="12" t="n"/>
       <c r="F8" s="12" t="n"/>
@@ -684,7 +743,11 @@
           <t>Build passage rows from a payload.</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="12" t="n"/>
       <c r="F9" s="12" t="n"/>
@@ -700,7 +763,11 @@
           <t>Curate candidate_seed rows (tag/decide/split/delete).</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="12" t="n"/>
       <c r="F10" s="12" t="n"/>
@@ -716,7 +783,11 @@
           <t>candidate_seed quality-check report.</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="12" t="n"/>
       <c r="F11" s="12" t="n"/>
@@ -732,7 +803,11 @@
           <t>Generate a chapter-level output.</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
       <c r="D12" s="12" t="n"/>
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="12" t="n"/>
@@ -748,7 +823,11 @@
           <t>Assign strongs to M-code clusters / validate assignment.</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="12" t="n"/>
       <c r="F13" s="12" t="n"/>
@@ -764,7 +843,11 @@
           <t>Cluster overview report.</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n"/>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="12" t="n"/>
       <c r="F14" s="12" t="n"/>
@@ -780,7 +863,11 @@
           <t>THE sanctioned path for changing a cfg_* row.</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="12" t="n"/>
       <c r="F15" s="12" t="n"/>
@@ -796,7 +883,11 @@
           <t>Rebuild the content search index.</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n"/>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="12" t="n"/>
@@ -812,7 +903,11 @@
           <t>Query the content search index.</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n"/>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D17" s="12" t="n"/>
       <c r="E17" s="12" t="n"/>
       <c r="F17" s="12" t="n"/>
@@ -828,7 +923,11 @@
           <t>Size-profile the content index.</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n"/>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D18" s="12" t="n"/>
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="12" t="n"/>
@@ -844,7 +943,11 @@
           <t>Create/replace a named SQLite view in iba.db.</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n"/>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
+        </is>
+      </c>
       <c r="D19" s="12" t="n"/>
       <c r="E19" s="12" t="n"/>
       <c r="F19" s="12" t="n"/>
@@ -860,7 +963,11 @@
           <t>Create vw_passage_verse_top10 and export it to CSV.</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n"/>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
+        </is>
+      </c>
       <c r="D20" s="12" t="n"/>
       <c r="E20" s="12" t="n"/>
       <c r="F20" s="12" t="n"/>
@@ -876,7 +983,11 @@
           <t>Create vw_passages_by_book (scoped to one book) and export it.</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
+        </is>
+      </c>
       <c r="D21" s="12" t="n"/>
       <c r="E21" s="12" t="n"/>
       <c r="F21" s="12" t="n"/>
@@ -892,7 +1003,11 @@
           <t>The debate pipeline (HIB/phenomenon/operation/closing) for a book.</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
+        </is>
+      </c>
       <c r="D22" s="12" t="n"/>
       <c r="E22" s="12" t="n"/>
       <c r="F22" s="12" t="n"/>
@@ -908,7 +1023,11 @@
           <t>See the researcher's own model sheet, 'escalation actions worksheet.xlsx' -- not rebuilt here, this tab is a pointer only.</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n"/>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D23" s="12" t="n"/>
       <c r="E23" s="12" t="n"/>
       <c r="F23" s="12" t="n"/>
@@ -924,7 +1043,11 @@
           <t>Export all cfg_* tables to CSV + an index report.</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
+        </is>
+      </c>
       <c r="D24" s="12" t="n"/>
       <c r="E24" s="12" t="n"/>
       <c r="F24" s="12" t="n"/>
@@ -940,7 +1063,11 @@
           <t>Export one or more cfg_*/data tables to CSV.</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D25" s="12" t="n"/>
       <c r="E25" s="12" t="n"/>
       <c r="F25" s="12" t="n"/>
@@ -956,7 +1083,11 @@
           <t>The folder_purpose governance mechanism (Methods A-D).</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n"/>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D26" s="12" t="n"/>
       <c r="E26" s="12" t="n"/>
       <c r="F26" s="12" t="n"/>
@@ -972,7 +1103,11 @@
           <t>Generate the full iba.db schema overview doc.</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n"/>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
+        </is>
+      </c>
       <c r="D27" s="12" t="n"/>
       <c r="E27" s="12" t="n"/>
       <c r="F27" s="12" t="n"/>
@@ -988,7 +1123,11 @@
           <t>Parse strong_lexicon / related-word data.</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n"/>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D28" s="12" t="n"/>
       <c r="E28" s="12" t="n"/>
       <c r="F28" s="12" t="n"/>
@@ -1004,7 +1143,11 @@
           <t>Apply log-retention rules (prune old logs).</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n"/>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D29" s="12" t="n"/>
       <c r="E29" s="12" t="n"/>
       <c r="F29" s="12" t="n"/>
@@ -1020,7 +1163,11 @@
           <t>Rebuild the file_manifest table.</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n"/>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D30" s="12" t="n"/>
       <c r="E30" s="12" t="n"/>
       <c r="F30" s="12" t="n"/>
@@ -1036,7 +1183,11 @@
           <t>Search the file_manifest table.</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n"/>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D31" s="12" t="n"/>
       <c r="E31" s="12" t="n"/>
       <c r="F31" s="12" t="n"/>
@@ -1052,7 +1203,11 @@
           <t>Register a new word_registry entry and run its first-pass pipeline.</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n"/>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D32" s="12" t="n"/>
       <c r="E32" s="12" t="n"/>
       <c r="F32" s="12" t="n"/>
@@ -1068,7 +1223,11 @@
           <t>Ingest a debate-step payload (hib/phenomenon/operation/closing).</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n"/>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D33" s="12" t="n"/>
       <c r="E33" s="12" t="n"/>
       <c r="F33" s="12" t="n"/>
@@ -1084,7 +1243,11 @@
           <t>Quality-check passages, optionally scoped to a book.</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n"/>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D34" s="12" t="n"/>
       <c r="E34" s="12" t="n"/>
       <c r="F34" s="12" t="n"/>
@@ -1100,7 +1263,11 @@
           <t>Report on passage/debate state for a book.</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n"/>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
       <c r="D35" s="12" t="n"/>
       <c r="E35" s="12" t="n"/>
       <c r="F35" s="12" t="n"/>
@@ -1116,7 +1283,11 @@
           <t>Sync file-based debate output back into passage/phenomenon.</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n"/>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
       <c r="D36" s="12" t="n"/>
       <c r="E36" s="12" t="n"/>
       <c r="F36" s="12" t="n"/>
@@ -1132,7 +1303,11 @@
           <t>Scan for hardcoded paths that should be config-driven.</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n"/>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D37" s="12" t="n"/>
       <c r="E37" s="12" t="n"/>
       <c r="F37" s="12" t="n"/>
@@ -1148,7 +1323,11 @@
           <t>Prose store: extract/search/export/import/flag/status the programme prose.</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n"/>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D38" s="12" t="n"/>
       <c r="E38" s="12" t="n"/>
       <c r="F38" s="12" t="n"/>
@@ -1164,7 +1343,11 @@
           <t>Backfill span/strong_verse from raw span data for a book.</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n"/>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D39" s="12" t="n"/>
       <c r="E39" s="12" t="n"/>
       <c r="F39" s="12" t="n"/>
@@ -1180,7 +1363,11 @@
           <t>word_registry overview report.</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n"/>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D40" s="12" t="n"/>
       <c r="E40" s="12" t="n"/>
       <c r="F40" s="12" t="n"/>
@@ -1196,7 +1383,11 @@
           <t>Word/book validation and report bundle.</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n"/>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D41" s="12" t="n"/>
       <c r="E41" s="12" t="n"/>
       <c r="F41" s="12" t="n"/>
@@ -1212,7 +1403,11 @@
           <t>Live iba.db schema overview report.</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n"/>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D42" s="12" t="n"/>
       <c r="E42" s="12" t="n"/>
       <c r="F42" s="12" t="n"/>
@@ -1228,7 +1423,11 @@
           <t>candidate_seed coverage report.</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n"/>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
       <c r="D43" s="12" t="n"/>
       <c r="E43" s="12" t="n"/>
       <c r="F43" s="12" t="n"/>
@@ -1244,7 +1443,11 @@
           <t>Seed candidate_seed rows for a book.</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n"/>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
       <c r="D44" s="12" t="n"/>
       <c r="E44" s="12" t="n"/>
       <c r="F44" s="12" t="n"/>
@@ -1260,7 +1463,11 @@
           <t>span table analysis report.</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n"/>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D45" s="12" t="n"/>
       <c r="E45" s="12" t="n"/>
       <c r="F45" s="12" t="n"/>
@@ -1276,7 +1483,11 @@
           <t>Session bootstrap -- run once per session before any IBA work.</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n"/>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
+        </is>
+      </c>
       <c r="D46" s="12" t="n"/>
       <c r="E46" s="12" t="n"/>
       <c r="F46" s="12" t="n"/>
@@ -1292,7 +1503,11 @@
           <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n"/>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D47" s="12" t="n"/>
       <c r="E47" s="12" t="n"/>
       <c r="F47" s="12" t="n"/>
@@ -1308,7 +1523,11 @@
           <t>Report a word's strong&lt;-&gt;verse coverage.</t>
         </is>
       </c>
-      <c r="C48" s="12" t="n"/>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D48" s="12" t="n"/>
       <c r="E48" s="12" t="n"/>
       <c r="F48" s="12" t="n"/>
@@ -1324,7 +1543,11 @@
           <t>Run verse_lexical (L4b) derivation for a book/chapter range.</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n"/>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D49" s="12" t="n"/>
       <c r="E49" s="12" t="n"/>
       <c r="F49" s="12" t="n"/>
@@ -1340,7 +1563,11 @@
           <t>Report verse-span-meaning coverage for a book.</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n"/>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
       <c r="D50" s="12" t="n"/>
       <c r="E50" s="12" t="n"/>
       <c r="F50" s="12" t="n"/>
@@ -1356,7 +1583,11 @@
           <t>Whole-book-read report for a book.</t>
         </is>
       </c>
-      <c r="C51" s="12" t="n"/>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D51" s="12" t="n"/>
       <c r="E51" s="12" t="n"/>
       <c r="F51" s="12" t="n"/>
@@ -1372,7 +1603,11 @@
           <t>Report a word's span coverage against its registry entry.</t>
         </is>
       </c>
-      <c r="C52" s="12" t="n"/>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="D52" s="12" t="n"/>
       <c r="E52" s="12" t="n"/>
       <c r="F52" s="12" t="n"/>
@@ -6410,6 +6645,73 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34.005" customWidth="1" min="1" max="1"/>
+    <col width="60.005" customWidth="1" min="2" max="2"/>
+    <col width="22.005" customWidth="1" min="3" max="3"/>
+    <col width="22.005" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Catalogue-Report.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Structural review of wa_obs_question_catalogue (bible_research.db) -- no findings/joins. Escalation #1007 second half. Read-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Catalogue-Report.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="20">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -57,6 +57,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WholeBookRead-Report" sheetId="49" state="visible" r:id="rId49"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WordRegistrySpan-Report" sheetId="50" state="visible" r:id="rId50"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Report" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Update" sheetId="52" state="visible" r:id="rId52"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -601,7 +602,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1487,6 +1488,23 @@
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Catalogue-Update.ps1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Validated partial UPDATE of one wa_obs_question_catalogue row by obs_id (source/last_modified/etc.). No history table.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -5589,6 +5607,114 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="10"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Catalogue-Update.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Validated partial UPDATE of one wa_obs_question_catalogue row (bible_research.db) by obs_id. Every column except obs_id settable; auto-fills last_modified/catalogue_version if not given. No history table -- researcher's own call, escalation #1007.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-ObsId</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Set</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>REQUIRED. The wa_obs_question_catalogue row to update.</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>REQUIRED. JSON object of column:value pairs, e.g. {"source":"verse_lexical.resolved_sense"}</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>resume/re-tag a specific run</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="17" t="n"/>
+      <c r="I5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Catalogue-Update.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -172,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -237,6 +237,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5097,7 +5101,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5105,6 +5109,7 @@
     <col width="22" bestFit="1" customWidth="1" min="3" max="7"/>
     <col width="11.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
     <col width="13.5703125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -5168,6 +5173,11 @@
           <t>-Step</t>
         </is>
       </c>
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t>-PayloadPath</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="51.75" customFormat="1" customHeight="1" s="18">
       <c r="D5" s="17" t="inlineStr">
@@ -5182,7 +5192,12 @@
       </c>
       <c r="I5" s="18" t="inlineStr">
         <is>
-          <t>lexical.build|report.verse_lexical -- omit to run both chained; report.verse_lexical alone VIEWS already-built results with no re-build</t>
+          <t>lexical.build|lexical.enrich|report.verse_lexical|report.lexical_exceptions|report.lexical_extract -- omit to run the full chained sequence (now also runs lexical.enrich + report.lexical_exceptions); report.verse_lexical alone VIEWS already-built results with no re-build</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>path to the lexical.enrich payload JSON (notes/remove/genre) -- REQUIRED when -Step lexical.enrich is used, or when running the full sequence (which now includes lexical.enrich)</t>
         </is>
       </c>
     </row>
@@ -5193,7 +5208,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")</f>
         <v/>
       </c>
       <c r="C6" s="18" t="inlineStr">
@@ -5721,12 +5736,14 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="22" bestFit="1" customWidth="1" min="3" max="7"/>
+    <col width="11.4" customWidth="1" min="8" max="8"/>
+    <col width="11.4" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -5780,6 +5797,16 @@
           <t>-Trace</t>
         </is>
       </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>-Suggest</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>-Confirm</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="F5" s="17" t="inlineStr">
@@ -5787,6 +5814,16 @@
           <t>path to the payload JSON</t>
         </is>
       </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>switch -- propose the next candidate passage boundary from cheap mechanical proxy signals (no table write, pauses for confirm/adjust); mutually exclusive with -Chapters/-Range</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>switch -- only with -Suggest: accept the suggestion verbatim, straight into passage.build (still needs -PayloadPath)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
@@ -5795,7 +5832,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
         <v/>
       </c>
     </row>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -5101,7 +5101,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5178,6 +5178,41 @@
           <t>-PayloadPath</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-SkipBuild</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-ForceRebuild</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-PassageFilter</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-VerseFilter</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-SurfaceFilter</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-StrongFilter</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>what this row demonstrates</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="51.75" customFormat="1" customHeight="1" s="18">
       <c r="D5" s="17" t="inlineStr">
@@ -5200,6 +5235,36 @@
           <t>path to the lexical.enrich payload JSON (notes/remove/genre) -- REQUIRED when -Step lexical.enrich is used, or when running the full sequence (which now includes lexical.enrich)</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>switch -- skip the lexical.build precheck/auto-build entirely, go straight to lexical.enrich (fails fast if Layer 1 is missing for the range). Mutually exclusive with -ForceRebuild.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>switch -- force lexical.build to rebuild even though Layer 1 is already present for the range; WARNS if Layer 2 notes already exist for it (rebuild orphans them -- see BUILD.md #234). Mutually exclusive with -SkipBuild.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>(report.lexical_extract only) comma-list of passage ids.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>(report.lexical_extract only) comma-list of OSIS verses, or a same-book range, e.g. 'Rom.9.14' or 'Gen.1.1-Gen.1.10'. Different syntax from -Range (chapter:verse against -Book) -- this filter ignores -Book/-Chapters/-Range entirely.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>(report.lexical_extract only) comma-list of exact surface-text values.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>(report.lexical_extract only) comma-list of Strong's codes.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="32.25" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
@@ -5208,7 +5273,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6&lt;&gt;"",$K$4&amp;" ","")&amp;IF(L6&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")</f>
         <v/>
       </c>
       <c r="C6" s="18" t="inlineStr">
@@ -5220,6 +5285,268 @@
       <c r="E6" s="18" t="inlineStr">
         <is>
           <t>8:2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>lexical.build</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Layer 1 only (mechanical build) -- no payload needed. Fixed 2026-09-05: this row used to omit -Step, which now runs the FULL default sequence (incl. lexical.enrich) and fails without a payload -- exactly the error found live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>iba\app\ps\VerseLexical.ps1</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>A7&amp;" "&amp;IF(C7="","",$C$4&amp;" '"&amp;C7&amp;"' ")&amp;IF(D7="","",$D$4&amp;" '"&amp;D7&amp;"' ")&amp;IF(E7="","",$E$4&amp;" '"&amp;E7&amp;"' ")&amp;IF(F7="","",$F$4&amp;" '"&amp;F7&amp;"' ")&amp;IF(G7="","",$G$4&amp;" '"&amp;G7&amp;"' ")&amp;IF(H7&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I7="","",$I$4&amp;" '"&amp;I7&amp;"' ")&amp;IF(J7="","",$J$4&amp;" '"&amp;J7&amp;"' ")&amp;IF(K7&lt;&gt;"",$K$4&amp;" ","")&amp;IF(L7&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M7="","",$M$4&amp;" '"&amp;M7&amp;"' ")&amp;IF(N7="","",$N$4&amp;" '"&amp;N7&amp;"' ")&amp;IF(O7="","",$O$4&amp;" '"&amp;O7&amp;"' ")&amp;IF(P7="","",$P$4&amp;" '"&amp;P7&amp;"' ")</f>
+        <v/>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Rom</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8:2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>report.verse_lexical</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>View already-built Layer 1 results -- no rebuild, no STEP calls, no payload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>iba\app\ps\VerseLexical.ps1</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>A8&amp;" "&amp;IF(C8="","",$C$4&amp;" '"&amp;C8&amp;"' ")&amp;IF(D8="","",$D$4&amp;" '"&amp;D8&amp;"' ")&amp;IF(E8="","",$E$4&amp;" '"&amp;E8&amp;"' ")&amp;IF(F8="","",$F$4&amp;" '"&amp;F8&amp;"' ")&amp;IF(G8="","",$G$4&amp;" '"&amp;G8&amp;"' ")&amp;IF(H8&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I8="","",$I$4&amp;" '"&amp;I8&amp;"' ")&amp;IF(J8="","",$J$4&amp;" '"&amp;J8&amp;"' ")&amp;IF(K8&lt;&gt;"",$K$4&amp;" ","")&amp;IF(L8&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M8="","",$M$4&amp;" '"&amp;M8&amp;"' ")&amp;IF(N8="","",$N$4&amp;" '"&amp;N8&amp;"' ")&amp;IF(O8="","",$O$4&amp;" '"&amp;O8&amp;"' ")&amp;IF(P8="","",$P$4&amp;" '"&amp;P8&amp;"' ")</f>
+        <v/>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Rom</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>9:14</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>lexical.enrich</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>iba\docs\lexical-enrich-payload-example-rom-9-14-v1-20260905.json</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Layer 2 enrich using the real worked-example payload -- see lexical-enrich-payload-guide-v1-20260905.md for what's in it. Auto-builds Layer 1 first only if it isn't already there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>iba\app\ps\VerseLexical.ps1</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>A9&amp;" "&amp;IF(C9="","",$C$4&amp;" '"&amp;C9&amp;"' ")&amp;IF(D9="","",$D$4&amp;" '"&amp;D9&amp;"' ")&amp;IF(E9="","",$E$4&amp;" '"&amp;E9&amp;"' ")&amp;IF(F9="","",$F$4&amp;" '"&amp;F9&amp;"' ")&amp;IF(G9="","",$G$4&amp;" '"&amp;G9&amp;"' ")&amp;IF(H9&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I9="","",$I$4&amp;" '"&amp;I9&amp;"' ")&amp;IF(J9="","",$J$4&amp;" '"&amp;J9&amp;"' ")&amp;IF(K9&lt;&gt;"",$K$4&amp;" ","")&amp;IF(L9&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M9="","",$M$4&amp;" '"&amp;M9&amp;"' ")&amp;IF(N9="","",$N$4&amp;" '"&amp;N9&amp;"' ")&amp;IF(O9="","",$O$4&amp;" '"&amp;O9&amp;"' ")&amp;IF(P9="","",$P$4&amp;" '"&amp;P9&amp;"' ")</f>
+        <v/>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Rom</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9:14</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>lexical.enrich</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>iba\docs\lexical-enrich-payload-example-rom-9-14-v1-20260905.json</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>-SkipBuild: same enrich, but skip the Layer-1 precheck entirely (use when you already know Layer 1 is current).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>iba\app\ps\VerseLexical.ps1</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>A10&amp;" "&amp;IF(C10="","",$C$4&amp;" '"&amp;C10&amp;"' ")&amp;IF(D10="","",$D$4&amp;" '"&amp;D10&amp;"' ")&amp;IF(E10="","",$E$4&amp;" '"&amp;E10&amp;"' ")&amp;IF(F10="","",$F$4&amp;" '"&amp;F10&amp;"' ")&amp;IF(G10="","",$G$4&amp;" '"&amp;G10&amp;"' ")&amp;IF(H10&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I10="","",$I$4&amp;" '"&amp;I10&amp;"' ")&amp;IF(J10="","",$J$4&amp;" '"&amp;J10&amp;"' ")&amp;IF(K10&lt;&gt;"",$K$4&amp;" ","")&amp;IF(L10&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M10="","",$M$4&amp;" '"&amp;M10&amp;"' ")&amp;IF(N10="","",$N$4&amp;" '"&amp;N10&amp;"' ")&amp;IF(O10="","",$O$4&amp;" '"&amp;O10&amp;"' ")&amp;IF(P10="","",$P$4&amp;" '"&amp;P10&amp;"' ")</f>
+        <v/>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rom</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9:14</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>lexical.enrich</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>iba\docs\lexical-enrich-payload-example-rom-9-14-v1-20260905.json</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>-ForceRebuild: force Layer 1 to rebuild even though already present (rare -- prints a warning if Layer 2 notes already exist, since rebuilding could touch them).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>iba\app\ps\VerseLexical.ps1</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>A11&amp;" "&amp;IF(C11="","",$C$4&amp;" '"&amp;C11&amp;"' ")&amp;IF(D11="","",$D$4&amp;" '"&amp;D11&amp;"' ")&amp;IF(E11="","",$E$4&amp;" '"&amp;E11&amp;"' ")&amp;IF(F11="","",$F$4&amp;" '"&amp;F11&amp;"' ")&amp;IF(G11="","",$G$4&amp;" '"&amp;G11&amp;"' ")&amp;IF(H11&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I11="","",$I$4&amp;" '"&amp;I11&amp;"' ")&amp;IF(J11="","",$J$4&amp;" '"&amp;J11&amp;"' ")&amp;IF(K11&lt;&gt;"",$K$4&amp;" ","")&amp;IF(L11&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M11="","",$M$4&amp;" '"&amp;M11&amp;"' ")&amp;IF(N11="","",$N$4&amp;" '"&amp;N11&amp;"' ")&amp;IF(O11="","",$O$4&amp;" '"&amp;O11&amp;"' ")&amp;IF(P11="","",$P$4&amp;" '"&amp;P11&amp;"' ")</f>
+        <v/>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Rom</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9:14</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>report.lexical_exceptions</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Per-run self-audit for an already-enriched range: Layer 1 tally, Layer 2 dispositions, judgement calls, and the dangling-reference integrity check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>iba\app\ps\VerseLexical.ps1</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>A12&amp;" "&amp;IF(C12="","",$C$4&amp;" '"&amp;C12&amp;"' ")&amp;IF(D12="","",$D$4&amp;" '"&amp;D12&amp;"' ")&amp;IF(E12="","",$E$4&amp;" '"&amp;E12&amp;"' ")&amp;IF(F12="","",$F$4&amp;" '"&amp;F12&amp;"' ")&amp;IF(G12="","",$G$4&amp;" '"&amp;G12&amp;"' ")&amp;IF(H12&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I12="","",$I$4&amp;" '"&amp;I12&amp;"' ")&amp;IF(J12="","",$J$4&amp;" '"&amp;J12&amp;"' ")&amp;IF(K12&lt;&gt;"",$K$4&amp;" ","")&amp;IF(L12&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M12="","",$M$4&amp;" '"&amp;M12&amp;"' ")&amp;IF(N12="","",$N$4&amp;" '"&amp;N12&amp;"' ")&amp;IF(O12="","",$O$4&amp;" '"&amp;O12&amp;"' ")&amp;IF(P12="","",$P$4&amp;" '"&amp;P12&amp;"' ")</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Rom</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>report.lexical_extract</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Rom.9.14</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>report.lexical_extract: filter-driven, ignores -Book/-Chapters/-Range (still required by this script -- any value works, e.g. Rom/1:1 here). Needs at least one of -PassageFilter/-VerseFilter/-SurfaceFilter/-StrongFilter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>iba\app\ps\VerseLexical.ps1</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>A13&amp;" "&amp;IF(C13="","",$C$4&amp;" '"&amp;C13&amp;"' ")&amp;IF(D13="","",$D$4&amp;" '"&amp;D13&amp;"' ")&amp;IF(E13="","",$E$4&amp;" '"&amp;E13&amp;"' ")&amp;IF(F13="","",$F$4&amp;" '"&amp;F13&amp;"' ")&amp;IF(G13="","",$G$4&amp;" '"&amp;G13&amp;"' ")&amp;IF(H13&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I13="","",$I$4&amp;" '"&amp;I13&amp;"' ")&amp;IF(J13="","",$J$4&amp;" '"&amp;J13&amp;"' ")&amp;IF(K13&lt;&gt;"",$K$4&amp;" ","")&amp;IF(L13&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M13="","",$M$4&amp;" '"&amp;M13&amp;"' ")&amp;IF(N13="","",$N$4&amp;" '"&amp;N13&amp;"' ")&amp;IF(O13="","",$O$4&amp;" '"&amp;O13&amp;"' ")&amp;IF(P13="","",$P$4&amp;" '"&amp;P13&amp;"' ")</f>
+        <v/>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rom</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>9:14</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>iba\docs\lexical-enrich-payload-example-rom-9-14-v1-20260905.json</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Rom.9.14</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Full default sequence (no -Step): build + view + enrich + exceptions + extract, all 5 steps in one run. Needs BOTH -PayloadPath (for lexical.enrich) AND a filter (for report.lexical_extract, now both in the default sequence) -- omitting either fails fast.</t>
         </is>
       </c>
     </row>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -31,33 +31,34 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FolderPurpose" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="generate-iba-db-schema-report" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexicon-Parse" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log-Retention" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Rebuild" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Search" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New-Word" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operations-Ingest" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passage-Quality" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PassageDebate-Report" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PassageDebate-Sync" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PathAudit" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prose" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw-Backfill" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry-Report" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-Report" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-BibleRes" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeedCandidate-Report" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set-Candidates" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpanAnalysis-Report" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start-Iba" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongMeaning-Report" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongVerse-Report" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseLexical" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseSpanMeaning-Report" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WholeBookRead-Report" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WordRegistrySpan-Report" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Report" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Update" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spine-Check" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log-Retention" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Rebuild" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Search" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New-Word" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operations-Ingest" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passage-Quality" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PassageDebate-Report" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PassageDebate-Sync" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PathAudit" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prose" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw-Backfill" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry-Report" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-Report" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-BibleRes" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeedCandidate-Report" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set-Candidates" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpanAnalysis-Report" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start-Iba" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongMeaning-Report" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongVerse-Report" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseLexical" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseSpanMeaning-Report" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WholeBookRead-Report" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WordRegistrySpan-Report" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Report" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Update" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -606,7 +607,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1509,6 +1510,23 @@
         </is>
       </c>
       <c r="C55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Spine-Check.ps1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Base-data spine integrity + discoverability check (verse/span/strong sync, meaning-parse completeness). Triggered from start-project.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -3099,14 +3117,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Log-Retention.ps1</t>
+          <t>Spine-Check.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Apply log-retention rules (prune old logs).</t>
+          <t>Base-data spine integrity + discoverability check (verse/span/strong sync, meaning-parse completeness, FATAL if broken).</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3155,7 @@
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Log-Retention.ps1</t>
+          <t>iba\app\ps\Spine-Check.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -3170,14 +3188,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Manifest-Rebuild.ps1</t>
+          <t>Log-Retention.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Rebuild the file_manifest table.</t>
+          <t>Apply log-retention rules (prune old logs).</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3226,7 @@
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Manifest-Rebuild.ps1</t>
+          <t>iba\app\ps\Log-Retention.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -3225,6 +3243,77 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Manifest-Rebuild.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Rebuild the file_manifest table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Manifest-Rebuild.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3301,108 +3390,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New-Word.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Register a new word_registry entry and run its first-pass pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Word</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Source</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Fresh</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>the English word, e.g. compassion</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>why this word -- provenance note</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>ignore any partial prior run</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>print every config read</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\New-Word.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3495,6 +3482,108 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>New-Word.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Register a new word_registry entry and run its first-pass pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-Word</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Source</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Fresh</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>the English word, e.g. compassion</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>why this word -- provenance note</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>ignore any partial prior run</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>print every config read</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\New-Word.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3596,7 +3685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3673,97 +3762,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PassageDebate-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Report on passage/debate state for a book.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Chapters</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Range</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-BookLabel</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\PassageDebate-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3786,14 +3784,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PassageDebate-Sync.ps1</t>
+          <t>PassageDebate-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Sync file-based debate output back into passage/phenomenon.</t>
+          <t>Report on passage/debate state for a book.</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3842,7 @@
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\PassageDebate-Sync.ps1</t>
+          <t>iba\app\ps\PassageDebate-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -3861,6 +3859,97 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PassageDebate-Sync.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Sync file-based debate output back into passage/phenomenon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-Book</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Chapters</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Range</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-BookLabel</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\PassageDebate-Sync.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3942,7 +4031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -4174,7 +4263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -4261,7 +4350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -4332,7 +4421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -4414,77 +4503,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SchemaOverview-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Live iba.db schema overview report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="66.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\SchemaOverview-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4588,14 +4606,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SchemaOverview-BibleResearch-Report.ps1</t>
+          <t>SchemaOverview-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Live bible_research.db schema overview report -- merged against cfg_table/cfg_column, table+column level, discrepancies flagged.</t>
+          <t>Live iba.db schema overview report.</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4644,7 @@
     <row r="6" ht="66.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\SchemaOverview-BibleResearch-Report.ps1</t>
+          <t>iba\app\ps\SchemaOverview-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -4659,14 +4677,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SeedCandidate-Report.ps1</t>
+          <t>SchemaOverview-BibleResearch-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>candidate_seed coverage report.</t>
+          <t>Live bible_research.db schema overview report -- merged against cfg_table/cfg_column, table+column level, discrepancies flagged.</t>
         </is>
       </c>
     </row>
@@ -4694,10 +4712,10 @@
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+    <row r="6" ht="66.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\SeedCandidate-Report.ps1</t>
+          <t>iba\app\ps\SchemaOverview-BibleResearch-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -4730,14 +4748,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Set-Candidates.ps1</t>
+          <t>SeedCandidate-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Seed candidate_seed rows for a book.</t>
+          <t>candidate_seed coverage report.</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4773,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Book</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -4768,7 +4786,7 @@
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Set-Candidates.ps1</t>
+          <t>iba\app\ps\SeedCandidate-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -4801,14 +4819,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SpanAnalysis-Report.ps1</t>
+          <t>Set-Candidates.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>span table analysis report.</t>
+          <t>Seed candidate_seed rows for a book.</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4844,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-RunId</t>
+          <t>-Book</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -4839,7 +4857,7 @@
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\SpanAnalysis-Report.ps1</t>
+          <t>iba\app\ps\Set-Candidates.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -4872,14 +4890,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Start-Iba.ps1</t>
+          <t>SpanAnalysis-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Session bootstrap -- run once per session before any IBA work.</t>
+          <t>span table analysis report.</t>
         </is>
       </c>
     </row>
@@ -4897,35 +4915,24 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Reload</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-Reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>reseed config from source</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>full reset</t>
-        </is>
-      </c>
-    </row>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Start-Iba.ps1</t>
+          <t>iba\app\ps\SpanAnalysis-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -4954,14 +4961,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>StrongMeaning-Report.ps1</t>
+          <t>Start-Iba.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
+          <t>Session bootstrap -- run once per session before any IBA work.</t>
         </is>
       </c>
     </row>
@@ -4979,24 +4986,35 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-RunId</t>
+          <t>-Reload</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
+          <t>-Reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>reseed config from source</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>full reset</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\StrongMeaning-Report.ps1</t>
+          <t>iba\app\ps\Start-Iba.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -5009,6 +5027,77 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>StrongMeaning-Report.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\StrongMeaning-Report.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -5095,7 +5184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -5558,7 +5647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -5644,87 +5733,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>WholeBookRead-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Whole-book-read report for a book.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-BookLabel</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\WholeBookRead-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5813,6 +5821,87 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WholeBookRead-Report.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Whole-book-read report for a book.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-Book</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-BookLabel</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\WholeBookRead-Report.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5883,7 +5972,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5949,7 +6038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
